--- a/Contingencia_FRE_COOPENAE.xlsx
+++ b/Contingencia_FRE_COOPENAE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aseguroca-my.sharepoint.com/personal/rblanco_grupoasys_com/Documents/Sponsor/Coopenae/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ricardo.blanco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B7E5341-E430-4DA7-8F7E-029A4AF95BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4C64C6-6039-484E-B604-BFE96F64FE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_GoBack" localSheetId="2">'desempleo 1'!#REF!</definedName>
     <definedName name="_GoBack" localSheetId="0">Solicitud!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'desempleo 1'!$C$2:$O$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Solicitud!$A$1:$T$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Solicitud!$B$2:$T$76</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <fileRecoveryPr autoRecover="0"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="164">
   <si>
     <t>SEGURO COLECTIVO DE FRAUDE Y ROBO "PROTECCIÓN TOTAL PLUS"</t>
   </si>
@@ -812,9 +812,6 @@
       <t>En caso de que requiera el servicio de asistencia puede comunicarse al teléfono (+506) 4101-0000,  en donde también podrá solicitar informes actualizados de los proveedores que forman parte de la red de proveedores.
 Las comunicaciones relacionadas con esta Póliza serán enviadas por la Aseguradora directamente al Tomador y/o Asegurado, a la dirección indicada por ellos y que consta en este documento, o a la última dirección proporcionada a la Aseguradora. El Tomador y/o Asegurado deberá notificar a la Aseguradora cualquier cambio de dirección; de lo contrario, se considerará válida, para todos los efectos, la última dirección registrada.</t>
     </r>
-  </si>
-  <si>
-    <t>Ricardo</t>
   </si>
   <si>
     <t>Nacionales</t>
@@ -2334,10 +2331,150 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="68" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="62" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2348,20 +2485,117 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="49" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="47" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="72" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="67" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="67" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="62" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="68" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="50" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="63" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2372,14 +2606,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2388,12 +2614,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2421,238 +2641,159 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="68" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="62" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="49" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="47" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="72" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="67" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="67" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="62" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="68" xfId="24" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="50" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="63" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2677,155 +2818,11 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="25">
@@ -5021,6 +5018,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -5308,6 +5309,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DD9E7C9-8472-470F-A565-68FBC64A2E5E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:T76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5337,18 +5341,18 @@
     </row>
     <row r="2" spans="2:19" s="82" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="79"/>
-      <c r="C2" s="159" t="s">
+      <c r="C2" s="127" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
       <c r="M2" s="52"/>
       <c r="N2" s="52"/>
       <c r="O2" s="49"/>
@@ -5359,18 +5363,18 @@
     </row>
     <row r="3" spans="2:19" s="82" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="83"/>
-      <c r="C3" s="160" t="s">
+      <c r="C3" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
       <c r="M3" s="53"/>
       <c r="N3" s="53"/>
       <c r="O3" s="50"/>
@@ -5381,46 +5385,46 @@
     </row>
     <row r="4" spans="2:19" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="59"/>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="129" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="162"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="162"/>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
       <c r="S4" s="41"/>
     </row>
     <row r="5" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="59"/>
-      <c r="C5" s="110" t="s">
+      <c r="C5" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
       <c r="S5" s="41"/>
     </row>
     <row r="6" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5428,45 +5432,45 @@
       <c r="C6" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="104" t="s">
+      <c r="D6" s="166"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="180"/>
+      <c r="I6" s="181" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="102"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="165"/>
+      <c r="L6" s="165"/>
+      <c r="M6" s="165"/>
+      <c r="N6" s="165"/>
+      <c r="O6" s="165"/>
+      <c r="P6" s="165"/>
+      <c r="Q6" s="165"/>
+      <c r="R6" s="165"/>
       <c r="S6" s="41"/>
     </row>
     <row r="7" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="59"/>
-      <c r="C7" s="110" t="s">
+      <c r="C7" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="111"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111"/>
-      <c r="R7" s="111"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
       <c r="S7" s="41"/>
     </row>
     <row r="8" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5474,21 +5478,21 @@
       <c r="C8" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="164"/>
-      <c r="M8" s="164"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="164"/>
-      <c r="P8" s="164"/>
-      <c r="Q8" s="164"/>
-      <c r="R8" s="164"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
       <c r="S8" s="41"/>
     </row>
     <row r="9" spans="2:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5496,45 +5500,45 @@
       <c r="C9" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="183"/>
+      <c r="F9" s="183"/>
+      <c r="G9" s="183"/>
+      <c r="H9" s="183"/>
+      <c r="I9" s="183"/>
+      <c r="J9" s="184"/>
       <c r="K9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="106"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="106"/>
-      <c r="O9" s="106"/>
-      <c r="P9" s="106"/>
-      <c r="Q9" s="106"/>
-      <c r="R9" s="106"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="144"/>
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
       <c r="S9" s="41"/>
     </row>
     <row r="10" spans="2:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="59"/>
-      <c r="C10" s="110" t="s">
+      <c r="C10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="111"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="99"/>
       <c r="S10" s="41"/>
     </row>
     <row r="11" spans="2:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5542,22 +5546,22 @@
       <c r="C11" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
       <c r="F11" s="60" t="s">
         <v>128</v>
       </c>
       <c r="H11" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="107"/>
-      <c r="K11" s="107"/>
-      <c r="L11" s="107"/>
-      <c r="M11" s="107"/>
-      <c r="N11" s="107"/>
-      <c r="O11" s="107"/>
-      <c r="P11" s="107"/>
-      <c r="Q11" s="107"/>
+      <c r="J11" s="166"/>
+      <c r="K11" s="166"/>
+      <c r="L11" s="166"/>
+      <c r="M11" s="166"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="166"/>
+      <c r="P11" s="166"/>
+      <c r="Q11" s="166"/>
       <c r="R11" s="74" t="s">
         <v>128</v>
       </c>
@@ -5565,24 +5569,24 @@
     </row>
     <row r="12" spans="2:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="59"/>
-      <c r="C12" s="110" t="s">
+      <c r="C12" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="111"/>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="111"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
+      <c r="P12" s="99"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="99"/>
       <c r="S12" s="41"/>
     </row>
     <row r="13" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5590,27 +5594,23 @@
       <c r="C13" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="166" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="167"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="137"/>
       <c r="K13" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="165" t="s">
-        <v>147</v>
-      </c>
-      <c r="M13" s="165"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="165"/>
-      <c r="Q13" s="165"/>
-      <c r="R13" s="165"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
+      <c r="R13" s="135"/>
       <c r="S13" s="41"/>
     </row>
     <row r="14" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5618,23 +5618,23 @@
       <c r="C14" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="98"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="143"/>
       <c r="K14" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="L14" s="101"/>
-      <c r="M14" s="101"/>
-      <c r="N14" s="101"/>
-      <c r="O14" s="101"/>
-      <c r="P14" s="101"/>
-      <c r="Q14" s="101"/>
-      <c r="R14" s="101"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="134"/>
+      <c r="O14" s="134"/>
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
       <c r="S14" s="41"/>
     </row>
     <row r="15" spans="2:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5642,43 +5642,43 @@
       <c r="C15" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="106"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
       <c r="S15" s="41"/>
     </row>
     <row r="16" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="59"/>
-      <c r="C16" s="110" t="s">
+      <c r="C16" s="98" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="99"/>
       <c r="S16" s="41"/>
     </row>
     <row r="17" spans="2:20" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5686,29 +5686,29 @@
       <c r="C17" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="168" t="str">
+      <c r="D17" s="138">
         <f>+D13</f>
-        <v>Ricardo</v>
-      </c>
-      <c r="E17" s="169"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="169"/>
-      <c r="J17" s="170"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="139"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="140"/>
       <c r="K17" s="70" t="s">
         <v>13</v>
       </c>
       <c r="L17" s="70"/>
-      <c r="M17" s="171" t="str">
+      <c r="M17" s="141">
         <f>+L13</f>
-        <v>Nacionales</v>
-      </c>
-      <c r="N17" s="171"/>
-      <c r="O17" s="171"/>
-      <c r="P17" s="171"/>
-      <c r="Q17" s="171"/>
-      <c r="R17" s="171"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="141"/>
+      <c r="O17" s="141"/>
+      <c r="P17" s="141"/>
+      <c r="Q17" s="141"/>
+      <c r="R17" s="141"/>
       <c r="S17" s="41"/>
     </row>
     <row r="18" spans="2:20" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5716,26 +5716,26 @@
       <c r="C18" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="98"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="143"/>
       <c r="K18" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="L18" s="96">
+      <c r="L18" s="177">
         <f>+L14</f>
         <v>0</v>
       </c>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="96"/>
+      <c r="M18" s="177"/>
+      <c r="N18" s="177"/>
+      <c r="O18" s="177"/>
+      <c r="P18" s="177"/>
+      <c r="Q18" s="177"/>
+      <c r="R18" s="177"/>
       <c r="S18" s="41"/>
     </row>
     <row r="19" spans="2:20" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5743,25 +5743,23 @@
       <c r="C19" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="98"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="142"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="143"/>
       <c r="K19" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="L19" s="101" t="s">
-        <v>151</v>
-      </c>
-      <c r="M19" s="101"/>
-      <c r="N19" s="101"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="101"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="134"/>
+      <c r="N19" s="134"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="134"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="134"/>
       <c r="S19" s="41"/>
     </row>
     <row r="20" spans="2:20" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5769,153 +5767,151 @@
       <c r="C20" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="94" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="99" t="s">
+      <c r="D20" s="94"/>
+      <c r="E20" s="178" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="100"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="98"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="143"/>
       <c r="K20" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="97"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="97"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="142"/>
+      <c r="N20" s="142"/>
+      <c r="O20" s="142"/>
+      <c r="P20" s="142"/>
+      <c r="Q20" s="142"/>
+      <c r="R20" s="142"/>
       <c r="S20" s="41"/>
     </row>
     <row r="21" spans="2:20" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="59"/>
-      <c r="C21" s="172" t="s">
+      <c r="C21" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="173"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="173"/>
-      <c r="H21" s="173"/>
-      <c r="I21" s="173"/>
-      <c r="J21" s="173"/>
-      <c r="K21" s="173"/>
-      <c r="L21" s="173"/>
-      <c r="M21" s="173"/>
-      <c r="N21" s="173"/>
-      <c r="O21" s="173"/>
-      <c r="P21" s="173"/>
-      <c r="Q21" s="173"/>
-      <c r="R21" s="173"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="146"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="146"/>
+      <c r="O21" s="146"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="146"/>
       <c r="S21" s="41"/>
     </row>
     <row r="22" spans="2:20" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="59"/>
-      <c r="C22" s="110" t="s">
+      <c r="C22" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="111"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="99"/>
+      <c r="P22" s="99"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="99"/>
       <c r="S22" s="41"/>
     </row>
     <row r="23" spans="2:20" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="59"/>
-      <c r="C23" s="143" t="s">
+      <c r="C23" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="144"/>
-      <c r="L23" s="144"/>
-      <c r="M23" s="144"/>
-      <c r="N23" s="144"/>
-      <c r="O23" s="144"/>
-      <c r="P23" s="144"/>
-      <c r="Q23" s="144"/>
-      <c r="R23" s="144"/>
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="106"/>
+      <c r="N23" s="106"/>
+      <c r="O23" s="106"/>
+      <c r="P23" s="106"/>
+      <c r="Q23" s="106"/>
+      <c r="R23" s="106"/>
       <c r="S23" s="41"/>
     </row>
     <row r="24" spans="2:20" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="59"/>
-      <c r="C24" s="110" t="s">
+      <c r="C24" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="99"/>
+      <c r="N24" s="99"/>
+      <c r="O24" s="99"/>
+      <c r="P24" s="99"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="99"/>
       <c r="S24" s="51"/>
     </row>
     <row r="25" spans="2:20" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="59"/>
-      <c r="C25" s="188" t="s">
+      <c r="C25" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="189"/>
-      <c r="E25" s="189"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="189"/>
-      <c r="H25" s="189"/>
-      <c r="I25" s="189"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="189"/>
-      <c r="L25" s="190"/>
-      <c r="M25" s="124" t="s">
+      <c r="D25" s="120"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="120"/>
+      <c r="I25" s="120"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="120"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="162" t="s">
         <v>30</v>
       </c>
-      <c r="N25" s="125"/>
-      <c r="O25" s="125"/>
-      <c r="P25" s="125"/>
-      <c r="Q25" s="125"/>
-      <c r="R25" s="126"/>
+      <c r="N25" s="163"/>
+      <c r="O25" s="163"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="164"/>
       <c r="S25" s="51"/>
     </row>
     <row r="26" spans="2:20" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="59"/>
-      <c r="C26" s="191"/>
-      <c r="D26" s="192"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="192"/>
-      <c r="G26" s="192"/>
-      <c r="H26" s="192"/>
-      <c r="I26" s="192"/>
-      <c r="J26" s="192"/>
-      <c r="K26" s="192"/>
-      <c r="L26" s="193"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="123"/>
+      <c r="L26" s="124"/>
       <c r="M26" s="62" t="s">
         <v>133</v>
       </c>
@@ -5938,74 +5934,74 @@
     </row>
     <row r="27" spans="2:20" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="47"/>
-      <c r="C27" s="121" t="s">
+      <c r="C27" s="100" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="122"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="122"/>
-      <c r="J27" s="122"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="122"/>
-      <c r="M27" s="127">
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="101"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="125">
         <v>325000</v>
       </c>
-      <c r="N27" s="129">
+      <c r="N27" s="167">
         <v>650000</v>
       </c>
-      <c r="O27" s="131">
+      <c r="O27" s="169">
         <v>1950000</v>
       </c>
-      <c r="P27" s="132">
+      <c r="P27" s="170">
         <v>3250000</v>
       </c>
-      <c r="Q27" s="132">
+      <c r="Q27" s="170">
         <v>6500000</v>
       </c>
-      <c r="R27" s="133">
+      <c r="R27" s="171">
         <v>9250000</v>
       </c>
       <c r="S27" s="41"/>
     </row>
     <row r="28" spans="2:20" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="47"/>
-      <c r="C28" s="121" t="s">
+      <c r="C28" s="100" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="122"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="122"/>
-      <c r="G28" s="122"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="122"/>
-      <c r="J28" s="122"/>
-      <c r="K28" s="122"/>
-      <c r="L28" s="122"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="130"/>
-      <c r="O28" s="130"/>
-      <c r="P28" s="128"/>
-      <c r="Q28" s="128"/>
-      <c r="R28" s="134"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="101"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="101"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="126"/>
+      <c r="N28" s="168"/>
+      <c r="O28" s="168"/>
+      <c r="P28" s="126"/>
+      <c r="Q28" s="126"/>
+      <c r="R28" s="172"/>
       <c r="S28" s="51"/>
     </row>
     <row r="29" spans="2:20" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="47"/>
-      <c r="C29" s="121" t="s">
+      <c r="C29" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="122"/>
-      <c r="J29" s="122"/>
-      <c r="K29" s="122"/>
-      <c r="L29" s="122"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="101"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="101"/>
       <c r="M29" s="63">
         <v>65000</v>
       </c>
@@ -6028,127 +6024,127 @@
     </row>
     <row r="30" spans="2:20" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="47"/>
-      <c r="C30" s="121" t="s">
+      <c r="C30" s="100" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="122"/>
-      <c r="G30" s="122"/>
-      <c r="H30" s="122"/>
-      <c r="I30" s="122"/>
-      <c r="J30" s="122"/>
-      <c r="K30" s="122"/>
-      <c r="L30" s="122"/>
-      <c r="M30" s="127">
+      <c r="D30" s="101"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="125">
         <v>162500</v>
       </c>
-      <c r="N30" s="132">
+      <c r="N30" s="170">
         <v>325000</v>
       </c>
-      <c r="O30" s="136">
+      <c r="O30" s="174">
         <v>650000</v>
       </c>
-      <c r="P30" s="129">
+      <c r="P30" s="167">
         <v>1300000</v>
       </c>
-      <c r="Q30" s="132">
+      <c r="Q30" s="170">
         <v>1950000</v>
       </c>
-      <c r="R30" s="135">
+      <c r="R30" s="173">
         <v>2500000</v>
       </c>
       <c r="S30" s="41"/>
     </row>
     <row r="31" spans="2:20" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="47"/>
-      <c r="C31" s="163" t="s">
+      <c r="C31" s="131" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="123"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="123"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="123"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="123"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="128"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="130"/>
-      <c r="Q31" s="128"/>
-      <c r="R31" s="134"/>
+      <c r="D31" s="132"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="132"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="132"/>
+      <c r="M31" s="126"/>
+      <c r="N31" s="126"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="168"/>
+      <c r="Q31" s="126"/>
+      <c r="R31" s="172"/>
       <c r="S31" s="41"/>
       <c r="T31" s="59"/>
     </row>
     <row r="32" spans="2:20" ht="14.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="47"/>
-      <c r="C32" s="121" t="s">
+      <c r="C32" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="122"/>
-      <c r="G32" s="122"/>
-      <c r="H32" s="122"/>
-      <c r="I32" s="122"/>
-      <c r="J32" s="122"/>
-      <c r="K32" s="122"/>
-      <c r="L32" s="180"/>
-      <c r="M32" s="174" t="s">
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="147" t="s">
         <v>131</v>
       </c>
-      <c r="N32" s="175"/>
-      <c r="O32" s="175"/>
-      <c r="P32" s="175"/>
-      <c r="Q32" s="175"/>
-      <c r="R32" s="176"/>
+      <c r="N32" s="148"/>
+      <c r="O32" s="148"/>
+      <c r="P32" s="148"/>
+      <c r="Q32" s="148"/>
+      <c r="R32" s="149"/>
       <c r="S32" s="51"/>
     </row>
     <row r="33" spans="2:20" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="47"/>
-      <c r="C33" s="121" t="s">
+      <c r="C33" s="100" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="122"/>
-      <c r="G33" s="122"/>
-      <c r="H33" s="122"/>
-      <c r="I33" s="122"/>
-      <c r="J33" s="122"/>
-      <c r="K33" s="122"/>
-      <c r="L33" s="122"/>
-      <c r="M33" s="123"/>
-      <c r="N33" s="123"/>
-      <c r="O33" s="123"/>
-      <c r="P33" s="123"/>
-      <c r="Q33" s="123"/>
-      <c r="R33" s="123"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="101"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101"/>
+      <c r="M33" s="132"/>
+      <c r="N33" s="132"/>
+      <c r="O33" s="132"/>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="132"/>
+      <c r="R33" s="132"/>
       <c r="S33" s="41"/>
     </row>
     <row r="34" spans="2:20" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="47"/>
-      <c r="C34" s="110" t="s">
+      <c r="C34" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
-      <c r="F34" s="111"/>
-      <c r="G34" s="111"/>
-      <c r="H34" s="111"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="111"/>
-      <c r="K34" s="111"/>
-      <c r="L34" s="111"/>
-      <c r="M34" s="111"/>
-      <c r="N34" s="111"/>
-      <c r="O34" s="111"/>
-      <c r="P34" s="111"/>
-      <c r="Q34" s="111"/>
-      <c r="R34" s="111"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="99"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="99"/>
+      <c r="R34" s="99"/>
       <c r="S34" s="41"/>
     </row>
     <row r="35" spans="2:20" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -6156,18 +6152,18 @@
       <c r="C35" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="102"/>
-      <c r="E35" s="102"/>
+      <c r="D35" s="165"/>
+      <c r="E35" s="165"/>
       <c r="F35" s="60" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="J35" s="107"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="107"/>
+      <c r="J35" s="166"/>
+      <c r="K35" s="166"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="166"/>
       <c r="N35" s="61" t="s">
         <v>128</v>
       </c>
@@ -6177,65 +6173,65 @@
       <c r="S35" s="41"/>
     </row>
     <row r="36" spans="2:20" s="55" customFormat="1" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="177"/>
-      <c r="C36" s="110" t="s">
+      <c r="B36" s="95"/>
+      <c r="C36" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="99"/>
+      <c r="J36" s="99"/>
+      <c r="K36" s="99"/>
+      <c r="L36" s="99"/>
+      <c r="M36" s="99"/>
+      <c r="N36" s="99"/>
+      <c r="O36" s="99"/>
+      <c r="P36" s="99"/>
+      <c r="Q36" s="99"/>
+      <c r="R36" s="99"/>
       <c r="S36" s="43"/>
       <c r="T36" s="48"/>
     </row>
     <row r="37" spans="2:20" s="55" customFormat="1" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="177"/>
-      <c r="C37" s="110" t="s">
+      <c r="B37" s="95"/>
+      <c r="C37" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
-      <c r="F37" s="111"/>
-      <c r="G37" s="111"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="111"/>
-      <c r="N37" s="111"/>
-      <c r="O37" s="111"/>
-      <c r="P37" s="111"/>
-      <c r="Q37" s="111"/>
-      <c r="R37" s="111"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="99"/>
+      <c r="K37" s="99"/>
+      <c r="L37" s="99"/>
+      <c r="M37" s="99"/>
+      <c r="N37" s="99"/>
+      <c r="O37" s="99"/>
+      <c r="P37" s="99"/>
+      <c r="Q37" s="99"/>
+      <c r="R37" s="99"/>
       <c r="S37" s="43"/>
       <c r="T37" s="48"/>
     </row>
     <row r="38" spans="2:20" s="55" customFormat="1" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="177"/>
-      <c r="C38" s="178" t="s">
+      <c r="B38" s="95"/>
+      <c r="C38" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="179"/>
-      <c r="E38" s="179"/>
-      <c r="F38" s="179"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="179"/>
-      <c r="I38" s="179"/>
-      <c r="J38" s="179"/>
-      <c r="K38" s="179"/>
-      <c r="L38" s="179"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="97"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="97"/>
       <c r="M38" s="66">
         <v>4000</v>
       </c>
@@ -6258,109 +6254,109 @@
     </row>
     <row r="39" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="59"/>
-      <c r="C39" s="110"/>
-      <c r="D39" s="111"/>
-      <c r="E39" s="111"/>
-      <c r="F39" s="111"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="111"/>
-      <c r="M39" s="111"/>
-      <c r="N39" s="111"/>
-      <c r="O39" s="111"/>
-      <c r="P39" s="111"/>
-      <c r="Q39" s="111"/>
-      <c r="R39" s="111"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="99"/>
+      <c r="I39" s="99"/>
+      <c r="J39" s="99"/>
+      <c r="K39" s="99"/>
+      <c r="L39" s="99"/>
+      <c r="M39" s="99"/>
+      <c r="N39" s="99"/>
+      <c r="O39" s="99"/>
+      <c r="P39" s="99"/>
+      <c r="Q39" s="99"/>
+      <c r="R39" s="99"/>
       <c r="S39" s="44"/>
     </row>
     <row r="40" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="59"/>
-      <c r="C40" s="115" t="s">
+      <c r="C40" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="117" t="s">
+      <c r="D40" s="189"/>
+      <c r="E40" s="189"/>
+      <c r="F40" s="189"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="190" t="s">
         <v>36</v>
       </c>
-      <c r="L40" s="118"/>
-      <c r="M40" s="118"/>
-      <c r="N40" s="118"/>
-      <c r="O40" s="118"/>
-      <c r="P40" s="118"/>
-      <c r="Q40" s="118"/>
-      <c r="R40" s="118"/>
+      <c r="L40" s="191"/>
+      <c r="M40" s="191"/>
+      <c r="N40" s="191"/>
+      <c r="O40" s="191"/>
+      <c r="P40" s="191"/>
+      <c r="Q40" s="191"/>
+      <c r="R40" s="191"/>
       <c r="S40" s="44"/>
     </row>
     <row r="41" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="59"/>
-      <c r="C41" s="119" t="s">
+      <c r="C41" s="192" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="120"/>
-      <c r="E41" s="120"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="120"/>
-      <c r="J41" s="120"/>
-      <c r="K41" s="120"/>
-      <c r="L41" s="120"/>
-      <c r="M41" s="120"/>
-      <c r="N41" s="120"/>
-      <c r="O41" s="120"/>
-      <c r="P41" s="120"/>
-      <c r="Q41" s="120"/>
-      <c r="R41" s="120"/>
+      <c r="D41" s="193"/>
+      <c r="E41" s="193"/>
+      <c r="F41" s="193"/>
+      <c r="G41" s="193"/>
+      <c r="H41" s="193"/>
+      <c r="I41" s="193"/>
+      <c r="J41" s="193"/>
+      <c r="K41" s="193"/>
+      <c r="L41" s="193"/>
+      <c r="M41" s="193"/>
+      <c r="N41" s="193"/>
+      <c r="O41" s="193"/>
+      <c r="P41" s="193"/>
+      <c r="Q41" s="193"/>
+      <c r="R41" s="193"/>
       <c r="S41" s="44"/>
     </row>
     <row r="42" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="59"/>
-      <c r="C42" s="110" t="s">
+      <c r="C42" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="111"/>
-      <c r="E42" s="111"/>
-      <c r="F42" s="111"/>
-      <c r="G42" s="111"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="111"/>
-      <c r="J42" s="111"/>
-      <c r="K42" s="111"/>
-      <c r="L42" s="111"/>
-      <c r="M42" s="111"/>
-      <c r="N42" s="111"/>
-      <c r="O42" s="111"/>
-      <c r="P42" s="111"/>
-      <c r="Q42" s="111"/>
-      <c r="R42" s="111"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="99"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="99"/>
+      <c r="I42" s="99"/>
+      <c r="J42" s="99"/>
+      <c r="K42" s="99"/>
+      <c r="L42" s="99"/>
+      <c r="M42" s="99"/>
+      <c r="N42" s="99"/>
+      <c r="O42" s="99"/>
+      <c r="P42" s="99"/>
+      <c r="Q42" s="99"/>
+      <c r="R42" s="99"/>
       <c r="S42" s="44"/>
     </row>
     <row r="43" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="59"/>
-      <c r="C43" s="112" t="s">
+      <c r="C43" s="185" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="113"/>
-      <c r="E43" s="113"/>
-      <c r="F43" s="113"/>
-      <c r="G43" s="114"/>
+      <c r="D43" s="186"/>
+      <c r="E43" s="186"/>
+      <c r="F43" s="186"/>
+      <c r="G43" s="187"/>
       <c r="H43" s="72" t="s">
         <v>40</v>
       </c>
       <c r="I43" s="73"/>
-      <c r="J43" s="95"/>
-      <c r="K43" s="95"/>
-      <c r="L43" s="95"/>
-      <c r="M43" s="95"/>
+      <c r="J43" s="176"/>
+      <c r="K43" s="176"/>
+      <c r="L43" s="176"/>
+      <c r="M43" s="176"/>
       <c r="N43" s="73"/>
       <c r="O43" s="73"/>
       <c r="P43" s="73"/>
@@ -6370,571 +6366,571 @@
     </row>
     <row r="44" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="59"/>
-      <c r="C44" s="139" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" s="140"/>
-      <c r="E44" s="140"/>
-      <c r="F44" s="140"/>
-      <c r="G44" s="140"/>
-      <c r="H44" s="140"/>
-      <c r="I44" s="140"/>
-      <c r="J44" s="140"/>
-      <c r="K44" s="140"/>
-      <c r="L44" s="140"/>
-      <c r="M44" s="140"/>
-      <c r="N44" s="140"/>
-      <c r="O44" s="140"/>
-      <c r="P44" s="140"/>
-      <c r="Q44" s="140"/>
-      <c r="R44" s="140"/>
+      <c r="C44" s="150" t="s">
+        <v>158</v>
+      </c>
+      <c r="D44" s="151"/>
+      <c r="E44" s="151"/>
+      <c r="F44" s="151"/>
+      <c r="G44" s="151"/>
+      <c r="H44" s="151"/>
+      <c r="I44" s="151"/>
+      <c r="J44" s="151"/>
+      <c r="K44" s="151"/>
+      <c r="L44" s="151"/>
+      <c r="M44" s="151"/>
+      <c r="N44" s="151"/>
+      <c r="O44" s="151"/>
+      <c r="P44" s="151"/>
+      <c r="Q44" s="151"/>
+      <c r="R44" s="151"/>
       <c r="S44" s="44"/>
     </row>
     <row r="45" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="59"/>
-      <c r="C45" s="141" t="s">
+      <c r="C45" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="D45" s="142"/>
-      <c r="E45" s="142"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="142"/>
-      <c r="I45" s="142"/>
-      <c r="J45" s="142"/>
-      <c r="K45" s="142"/>
-      <c r="L45" s="142"/>
-      <c r="M45" s="142"/>
-      <c r="N45" s="142"/>
-      <c r="O45" s="142"/>
-      <c r="P45" s="142"/>
-      <c r="Q45" s="142"/>
-      <c r="R45" s="142"/>
+      <c r="D45" s="153"/>
+      <c r="E45" s="153"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="153"/>
+      <c r="H45" s="153"/>
+      <c r="I45" s="153"/>
+      <c r="J45" s="153"/>
+      <c r="K45" s="153"/>
+      <c r="L45" s="153"/>
+      <c r="M45" s="153"/>
+      <c r="N45" s="153"/>
+      <c r="O45" s="153"/>
+      <c r="P45" s="153"/>
+      <c r="Q45" s="153"/>
+      <c r="R45" s="153"/>
       <c r="S45" s="44"/>
     </row>
     <row r="46" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="59"/>
-      <c r="C46" s="110" t="s">
+      <c r="C46" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="111"/>
-      <c r="E46" s="111"/>
-      <c r="F46" s="111"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="111"/>
-      <c r="I46" s="111"/>
-      <c r="J46" s="111"/>
-      <c r="K46" s="111"/>
-      <c r="L46" s="111"/>
-      <c r="M46" s="111"/>
-      <c r="N46" s="111"/>
-      <c r="O46" s="111"/>
-      <c r="P46" s="111"/>
-      <c r="Q46" s="111"/>
-      <c r="R46" s="111"/>
+      <c r="D46" s="99"/>
+      <c r="E46" s="99"/>
+      <c r="F46" s="99"/>
+      <c r="G46" s="99"/>
+      <c r="H46" s="99"/>
+      <c r="I46" s="99"/>
+      <c r="J46" s="99"/>
+      <c r="K46" s="99"/>
+      <c r="L46" s="99"/>
+      <c r="M46" s="99"/>
+      <c r="N46" s="99"/>
+      <c r="O46" s="99"/>
+      <c r="P46" s="99"/>
+      <c r="Q46" s="99"/>
+      <c r="R46" s="99"/>
       <c r="S46" s="44"/>
     </row>
     <row r="47" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="59"/>
-      <c r="C47" s="143" t="s">
+      <c r="C47" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="D47" s="144"/>
-      <c r="E47" s="144"/>
-      <c r="F47" s="144"/>
-      <c r="G47" s="144"/>
-      <c r="H47" s="144"/>
-      <c r="I47" s="144"/>
-      <c r="J47" s="144"/>
-      <c r="K47" s="144"/>
-      <c r="L47" s="144"/>
-      <c r="M47" s="144"/>
-      <c r="N47" s="144"/>
-      <c r="O47" s="144"/>
-      <c r="P47" s="144"/>
-      <c r="Q47" s="144"/>
-      <c r="R47" s="144"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="106"/>
+      <c r="I47" s="106"/>
+      <c r="J47" s="106"/>
+      <c r="K47" s="106"/>
+      <c r="L47" s="106"/>
+      <c r="M47" s="106"/>
+      <c r="N47" s="106"/>
+      <c r="O47" s="106"/>
+      <c r="P47" s="106"/>
+      <c r="Q47" s="106"/>
+      <c r="R47" s="106"/>
       <c r="S47" s="44"/>
     </row>
     <row r="48" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="59"/>
-      <c r="C48" s="153" t="s">
+      <c r="C48" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="D48" s="154"/>
-      <c r="E48" s="154"/>
-      <c r="F48" s="154"/>
-      <c r="G48" s="154"/>
-      <c r="H48" s="154"/>
-      <c r="I48" s="154"/>
-      <c r="J48" s="154"/>
-      <c r="K48" s="154"/>
-      <c r="L48" s="154"/>
-      <c r="M48" s="154"/>
-      <c r="N48" s="154"/>
-      <c r="O48" s="154"/>
-      <c r="P48" s="154"/>
-      <c r="Q48" s="154"/>
-      <c r="R48" s="154"/>
+      <c r="D48" s="159"/>
+      <c r="E48" s="159"/>
+      <c r="F48" s="159"/>
+      <c r="G48" s="159"/>
+      <c r="H48" s="159"/>
+      <c r="I48" s="159"/>
+      <c r="J48" s="159"/>
+      <c r="K48" s="159"/>
+      <c r="L48" s="159"/>
+      <c r="M48" s="159"/>
+      <c r="N48" s="159"/>
+      <c r="O48" s="159"/>
+      <c r="P48" s="159"/>
+      <c r="Q48" s="159"/>
+      <c r="R48" s="159"/>
       <c r="S48" s="44"/>
     </row>
     <row r="49" spans="2:19" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="59"/>
-      <c r="C49" s="182" t="s">
+      <c r="C49" s="107" t="s">
         <v>145</v>
       </c>
-      <c r="D49" s="183"/>
-      <c r="E49" s="183"/>
-      <c r="F49" s="183"/>
-      <c r="G49" s="183"/>
-      <c r="H49" s="183"/>
-      <c r="I49" s="183"/>
-      <c r="J49" s="183"/>
-      <c r="K49" s="183"/>
-      <c r="L49" s="183"/>
-      <c r="M49" s="183"/>
-      <c r="N49" s="183"/>
-      <c r="O49" s="183"/>
-      <c r="P49" s="183"/>
-      <c r="Q49" s="183"/>
-      <c r="R49" s="183"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="108"/>
+      <c r="I49" s="108"/>
+      <c r="J49" s="108"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="108"/>
+      <c r="M49" s="108"/>
+      <c r="N49" s="108"/>
+      <c r="O49" s="108"/>
+      <c r="P49" s="108"/>
+      <c r="Q49" s="108"/>
+      <c r="R49" s="108"/>
       <c r="S49" s="44"/>
     </row>
     <row r="50" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="59"/>
-      <c r="C50" s="110" t="s">
+      <c r="C50" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="D50" s="111"/>
-      <c r="E50" s="111"/>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="111"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="111"/>
-      <c r="K50" s="111"/>
-      <c r="L50" s="111"/>
-      <c r="M50" s="111"/>
-      <c r="N50" s="111"/>
-      <c r="O50" s="111"/>
-      <c r="P50" s="111"/>
-      <c r="Q50" s="111"/>
-      <c r="R50" s="111"/>
+      <c r="D50" s="99"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="99"/>
+      <c r="H50" s="99"/>
+      <c r="I50" s="99"/>
+      <c r="J50" s="99"/>
+      <c r="K50" s="99"/>
+      <c r="L50" s="99"/>
+      <c r="M50" s="99"/>
+      <c r="N50" s="99"/>
+      <c r="O50" s="99"/>
+      <c r="P50" s="99"/>
+      <c r="Q50" s="99"/>
+      <c r="R50" s="99"/>
       <c r="S50" s="44"/>
     </row>
     <row r="51" spans="2:19" ht="39.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="59"/>
-      <c r="C51" s="143" t="s">
+      <c r="C51" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="D51" s="144"/>
-      <c r="E51" s="144"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="144"/>
-      <c r="H51" s="144"/>
-      <c r="I51" s="144"/>
-      <c r="J51" s="144"/>
-      <c r="K51" s="144"/>
-      <c r="L51" s="144"/>
-      <c r="M51" s="144"/>
-      <c r="N51" s="144"/>
-      <c r="O51" s="144"/>
-      <c r="P51" s="144"/>
-      <c r="Q51" s="144"/>
-      <c r="R51" s="144"/>
+      <c r="D51" s="106"/>
+      <c r="E51" s="106"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="106"/>
+      <c r="H51" s="106"/>
+      <c r="I51" s="106"/>
+      <c r="J51" s="106"/>
+      <c r="K51" s="106"/>
+      <c r="L51" s="106"/>
+      <c r="M51" s="106"/>
+      <c r="N51" s="106"/>
+      <c r="O51" s="106"/>
+      <c r="P51" s="106"/>
+      <c r="Q51" s="106"/>
+      <c r="R51" s="106"/>
       <c r="S51" s="44"/>
     </row>
     <row r="52" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="59"/>
-      <c r="C52" s="151" t="s">
+      <c r="C52" s="156" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="152"/>
-      <c r="E52" s="152"/>
-      <c r="F52" s="152"/>
-      <c r="G52" s="152"/>
-      <c r="H52" s="152"/>
-      <c r="I52" s="152"/>
-      <c r="J52" s="152"/>
-      <c r="K52" s="152"/>
-      <c r="L52" s="152"/>
-      <c r="M52" s="152"/>
-      <c r="N52" s="152"/>
-      <c r="O52" s="152"/>
-      <c r="P52" s="152"/>
-      <c r="Q52" s="152"/>
-      <c r="R52" s="152"/>
+      <c r="D52" s="157"/>
+      <c r="E52" s="157"/>
+      <c r="F52" s="157"/>
+      <c r="G52" s="157"/>
+      <c r="H52" s="157"/>
+      <c r="I52" s="157"/>
+      <c r="J52" s="157"/>
+      <c r="K52" s="157"/>
+      <c r="L52" s="157"/>
+      <c r="M52" s="157"/>
+      <c r="N52" s="157"/>
+      <c r="O52" s="157"/>
+      <c r="P52" s="157"/>
+      <c r="Q52" s="157"/>
+      <c r="R52" s="157"/>
       <c r="S52" s="44"/>
     </row>
     <row r="53" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="59"/>
-      <c r="C53" s="145" t="s">
+      <c r="C53" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="146"/>
-      <c r="E53" s="146"/>
-      <c r="F53" s="146"/>
-      <c r="G53" s="146"/>
-      <c r="H53" s="146"/>
-      <c r="I53" s="146"/>
-      <c r="J53" s="146"/>
-      <c r="K53" s="146"/>
-      <c r="L53" s="146"/>
-      <c r="M53" s="146"/>
-      <c r="N53" s="146"/>
-      <c r="O53" s="146"/>
-      <c r="P53" s="146"/>
-      <c r="Q53" s="146"/>
-      <c r="R53" s="146"/>
+      <c r="D53" s="114"/>
+      <c r="E53" s="114"/>
+      <c r="F53" s="114"/>
+      <c r="G53" s="114"/>
+      <c r="H53" s="114"/>
+      <c r="I53" s="114"/>
+      <c r="J53" s="114"/>
+      <c r="K53" s="114"/>
+      <c r="L53" s="114"/>
+      <c r="M53" s="114"/>
+      <c r="N53" s="114"/>
+      <c r="O53" s="114"/>
+      <c r="P53" s="114"/>
+      <c r="Q53" s="114"/>
+      <c r="R53" s="114"/>
       <c r="S53" s="44"/>
     </row>
     <row r="54" spans="2:19" ht="30.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="59"/>
-      <c r="C54" s="143" t="s">
+      <c r="C54" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="D54" s="144"/>
-      <c r="E54" s="144"/>
-      <c r="F54" s="144"/>
-      <c r="G54" s="144"/>
-      <c r="H54" s="144"/>
-      <c r="I54" s="144"/>
-      <c r="J54" s="144"/>
-      <c r="K54" s="144"/>
-      <c r="L54" s="144"/>
-      <c r="M54" s="144"/>
-      <c r="N54" s="144"/>
-      <c r="O54" s="144"/>
-      <c r="P54" s="144"/>
-      <c r="Q54" s="144"/>
-      <c r="R54" s="144"/>
+      <c r="D54" s="106"/>
+      <c r="E54" s="106"/>
+      <c r="F54" s="106"/>
+      <c r="G54" s="106"/>
+      <c r="H54" s="106"/>
+      <c r="I54" s="106"/>
+      <c r="J54" s="106"/>
+      <c r="K54" s="106"/>
+      <c r="L54" s="106"/>
+      <c r="M54" s="106"/>
+      <c r="N54" s="106"/>
+      <c r="O54" s="106"/>
+      <c r="P54" s="106"/>
+      <c r="Q54" s="106"/>
+      <c r="R54" s="106"/>
       <c r="S54" s="44"/>
     </row>
     <row r="55" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="59"/>
-      <c r="C55" s="110" t="s">
+      <c r="C55" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="D55" s="111"/>
-      <c r="E55" s="111"/>
-      <c r="F55" s="111"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="111"/>
-      <c r="I55" s="111"/>
-      <c r="J55" s="111"/>
-      <c r="K55" s="111"/>
-      <c r="L55" s="111"/>
-      <c r="M55" s="111"/>
-      <c r="N55" s="111"/>
-      <c r="O55" s="111"/>
-      <c r="P55" s="111"/>
-      <c r="Q55" s="111"/>
-      <c r="R55" s="111"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="99"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="99"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="99"/>
+      <c r="J55" s="99"/>
+      <c r="K55" s="99"/>
+      <c r="L55" s="99"/>
+      <c r="M55" s="99"/>
+      <c r="N55" s="99"/>
+      <c r="O55" s="99"/>
+      <c r="P55" s="99"/>
+      <c r="Q55" s="99"/>
+      <c r="R55" s="99"/>
       <c r="S55" s="44"/>
     </row>
     <row r="56" spans="2:19" ht="180" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="59"/>
-      <c r="C56" s="149" t="s">
+      <c r="C56" s="115" t="s">
         <v>144</v>
       </c>
-      <c r="D56" s="150"/>
-      <c r="E56" s="150"/>
-      <c r="F56" s="150"/>
-      <c r="G56" s="150"/>
-      <c r="H56" s="150"/>
-      <c r="I56" s="150"/>
-      <c r="J56" s="150"/>
-      <c r="K56" s="150"/>
-      <c r="L56" s="150"/>
-      <c r="M56" s="150"/>
-      <c r="N56" s="150"/>
-      <c r="O56" s="150"/>
-      <c r="P56" s="150"/>
-      <c r="Q56" s="150"/>
-      <c r="R56" s="150"/>
+      <c r="D56" s="116"/>
+      <c r="E56" s="116"/>
+      <c r="F56" s="116"/>
+      <c r="G56" s="116"/>
+      <c r="H56" s="116"/>
+      <c r="I56" s="116"/>
+      <c r="J56" s="116"/>
+      <c r="K56" s="116"/>
+      <c r="L56" s="116"/>
+      <c r="M56" s="116"/>
+      <c r="N56" s="116"/>
+      <c r="O56" s="116"/>
+      <c r="P56" s="116"/>
+      <c r="Q56" s="116"/>
+      <c r="R56" s="116"/>
       <c r="S56" s="44"/>
     </row>
     <row r="57" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="59"/>
-      <c r="C57" s="145" t="s">
+      <c r="C57" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D57" s="146"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="146"/>
-      <c r="G57" s="146"/>
-      <c r="H57" s="146"/>
-      <c r="I57" s="146"/>
-      <c r="J57" s="146"/>
-      <c r="K57" s="146"/>
-      <c r="L57" s="146"/>
-      <c r="M57" s="146"/>
-      <c r="N57" s="146"/>
-      <c r="O57" s="146"/>
-      <c r="P57" s="146"/>
-      <c r="Q57" s="146"/>
-      <c r="R57" s="146"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
+      <c r="H57" s="114"/>
+      <c r="I57" s="114"/>
+      <c r="J57" s="114"/>
+      <c r="K57" s="114"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="114"/>
+      <c r="N57" s="114"/>
+      <c r="O57" s="114"/>
+      <c r="P57" s="114"/>
+      <c r="Q57" s="114"/>
+      <c r="R57" s="114"/>
       <c r="S57" s="44"/>
     </row>
     <row r="58" spans="2:19" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="59"/>
-      <c r="C58" s="147" t="s">
+      <c r="C58" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="D58" s="148"/>
-      <c r="E58" s="148"/>
-      <c r="F58" s="148"/>
-      <c r="G58" s="148"/>
-      <c r="H58" s="148"/>
-      <c r="I58" s="148"/>
-      <c r="J58" s="148"/>
-      <c r="K58" s="148"/>
-      <c r="L58" s="148"/>
-      <c r="M58" s="148"/>
-      <c r="N58" s="148"/>
-      <c r="O58" s="148"/>
-      <c r="P58" s="148"/>
-      <c r="Q58" s="148"/>
-      <c r="R58" s="148"/>
+      <c r="D58" s="155"/>
+      <c r="E58" s="155"/>
+      <c r="F58" s="155"/>
+      <c r="G58" s="155"/>
+      <c r="H58" s="155"/>
+      <c r="I58" s="155"/>
+      <c r="J58" s="155"/>
+      <c r="K58" s="155"/>
+      <c r="L58" s="155"/>
+      <c r="M58" s="155"/>
+      <c r="N58" s="155"/>
+      <c r="O58" s="155"/>
+      <c r="P58" s="155"/>
+      <c r="Q58" s="155"/>
+      <c r="R58" s="155"/>
       <c r="S58" s="44"/>
     </row>
     <row r="59" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="59"/>
-      <c r="C59" s="110" t="s">
+      <c r="C59" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="D59" s="111"/>
-      <c r="E59" s="111"/>
-      <c r="F59" s="111"/>
-      <c r="G59" s="111"/>
-      <c r="H59" s="111"/>
-      <c r="I59" s="111"/>
-      <c r="J59" s="111"/>
-      <c r="K59" s="111"/>
-      <c r="L59" s="111"/>
-      <c r="M59" s="111"/>
-      <c r="N59" s="111"/>
-      <c r="O59" s="111"/>
-      <c r="P59" s="111"/>
-      <c r="Q59" s="111"/>
-      <c r="R59" s="111"/>
+      <c r="D59" s="99"/>
+      <c r="E59" s="99"/>
+      <c r="F59" s="99"/>
+      <c r="G59" s="99"/>
+      <c r="H59" s="99"/>
+      <c r="I59" s="99"/>
+      <c r="J59" s="99"/>
+      <c r="K59" s="99"/>
+      <c r="L59" s="99"/>
+      <c r="M59" s="99"/>
+      <c r="N59" s="99"/>
+      <c r="O59" s="99"/>
+      <c r="P59" s="99"/>
+      <c r="Q59" s="99"/>
+      <c r="R59" s="99"/>
       <c r="S59" s="44"/>
     </row>
     <row r="60" spans="2:19" ht="156.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="59"/>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="D60" s="150"/>
-      <c r="E60" s="150"/>
-      <c r="F60" s="150"/>
-      <c r="G60" s="150"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="150"/>
-      <c r="L60" s="150"/>
-      <c r="M60" s="150"/>
-      <c r="N60" s="150"/>
-      <c r="O60" s="150"/>
-      <c r="P60" s="150"/>
-      <c r="Q60" s="150"/>
-      <c r="R60" s="150"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="116"/>
+      <c r="L60" s="116"/>
+      <c r="M60" s="116"/>
+      <c r="N60" s="116"/>
+      <c r="O60" s="116"/>
+      <c r="P60" s="116"/>
+      <c r="Q60" s="116"/>
+      <c r="R60" s="116"/>
       <c r="S60" s="44"/>
     </row>
     <row r="61" spans="2:19" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="59"/>
-      <c r="C61" s="184" t="s">
-        <v>160</v>
-      </c>
-      <c r="D61" s="185"/>
-      <c r="E61" s="185"/>
-      <c r="F61" s="185"/>
-      <c r="G61" s="185"/>
-      <c r="H61" s="185"/>
-      <c r="I61" s="185"/>
-      <c r="J61" s="185"/>
-      <c r="K61" s="185"/>
-      <c r="L61" s="185"/>
-      <c r="M61" s="185"/>
-      <c r="N61" s="185"/>
-      <c r="O61" s="185"/>
-      <c r="P61" s="185"/>
-      <c r="Q61" s="185"/>
-      <c r="R61" s="185"/>
+      <c r="C61" s="111" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="112"/>
+      <c r="E61" s="112"/>
+      <c r="F61" s="112"/>
+      <c r="G61" s="112"/>
+      <c r="H61" s="112"/>
+      <c r="I61" s="112"/>
+      <c r="J61" s="112"/>
+      <c r="K61" s="112"/>
+      <c r="L61" s="112"/>
+      <c r="M61" s="112"/>
+      <c r="N61" s="112"/>
+      <c r="O61" s="112"/>
+      <c r="P61" s="112"/>
+      <c r="Q61" s="112"/>
+      <c r="R61" s="112"/>
       <c r="S61" s="44"/>
     </row>
     <row r="62" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="59"/>
-      <c r="C62" s="145" t="s">
+      <c r="C62" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="146"/>
-      <c r="E62" s="146"/>
-      <c r="F62" s="146"/>
-      <c r="G62" s="146"/>
-      <c r="H62" s="146"/>
-      <c r="I62" s="146"/>
-      <c r="J62" s="146"/>
-      <c r="K62" s="146"/>
-      <c r="L62" s="146"/>
-      <c r="M62" s="146"/>
-      <c r="N62" s="146"/>
-      <c r="O62" s="146"/>
-      <c r="P62" s="146"/>
-      <c r="Q62" s="146"/>
-      <c r="R62" s="146"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="114"/>
+      <c r="F62" s="114"/>
+      <c r="G62" s="114"/>
+      <c r="H62" s="114"/>
+      <c r="I62" s="114"/>
+      <c r="J62" s="114"/>
+      <c r="K62" s="114"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="114"/>
+      <c r="N62" s="114"/>
+      <c r="O62" s="114"/>
+      <c r="P62" s="114"/>
+      <c r="Q62" s="114"/>
+      <c r="R62" s="114"/>
       <c r="S62" s="44"/>
     </row>
     <row r="63" spans="2:19" ht="177.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="59"/>
-      <c r="C63" s="149" t="s">
+      <c r="C63" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="D63" s="150"/>
-      <c r="E63" s="150"/>
-      <c r="F63" s="150"/>
-      <c r="G63" s="150"/>
-      <c r="H63" s="150"/>
-      <c r="I63" s="150"/>
-      <c r="J63" s="150"/>
-      <c r="K63" s="150"/>
-      <c r="L63" s="150"/>
-      <c r="M63" s="150"/>
-      <c r="N63" s="150"/>
-      <c r="O63" s="150"/>
-      <c r="P63" s="150"/>
-      <c r="Q63" s="150"/>
-      <c r="R63" s="150"/>
+      <c r="D63" s="116"/>
+      <c r="E63" s="116"/>
+      <c r="F63" s="116"/>
+      <c r="G63" s="116"/>
+      <c r="H63" s="116"/>
+      <c r="I63" s="116"/>
+      <c r="J63" s="116"/>
+      <c r="K63" s="116"/>
+      <c r="L63" s="116"/>
+      <c r="M63" s="116"/>
+      <c r="N63" s="116"/>
+      <c r="O63" s="116"/>
+      <c r="P63" s="116"/>
+      <c r="Q63" s="116"/>
+      <c r="R63" s="116"/>
       <c r="S63" s="44"/>
     </row>
     <row r="64" spans="2:19" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="59"/>
-      <c r="C64" s="184" t="s">
+      <c r="C64" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="D64" s="185"/>
-      <c r="E64" s="185"/>
-      <c r="F64" s="185"/>
-      <c r="G64" s="185"/>
-      <c r="H64" s="185"/>
-      <c r="I64" s="185"/>
-      <c r="J64" s="185"/>
-      <c r="K64" s="185"/>
-      <c r="L64" s="185"/>
-      <c r="M64" s="185"/>
-      <c r="N64" s="185"/>
-      <c r="O64" s="185"/>
-      <c r="P64" s="185"/>
-      <c r="Q64" s="185"/>
-      <c r="R64" s="185"/>
+      <c r="D64" s="112"/>
+      <c r="E64" s="112"/>
+      <c r="F64" s="112"/>
+      <c r="G64" s="112"/>
+      <c r="H64" s="112"/>
+      <c r="I64" s="112"/>
+      <c r="J64" s="112"/>
+      <c r="K64" s="112"/>
+      <c r="L64" s="112"/>
+      <c r="M64" s="112"/>
+      <c r="N64" s="112"/>
+      <c r="O64" s="112"/>
+      <c r="P64" s="112"/>
+      <c r="Q64" s="112"/>
+      <c r="R64" s="112"/>
       <c r="S64" s="44"/>
     </row>
     <row r="65" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="59"/>
-      <c r="C65" s="145" t="s">
+      <c r="C65" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="D65" s="146"/>
-      <c r="E65" s="146"/>
-      <c r="F65" s="146"/>
-      <c r="G65" s="146"/>
-      <c r="H65" s="146"/>
-      <c r="I65" s="146"/>
-      <c r="J65" s="146"/>
-      <c r="K65" s="146"/>
-      <c r="L65" s="146"/>
-      <c r="M65" s="146"/>
-      <c r="N65" s="146"/>
-      <c r="O65" s="146"/>
-      <c r="P65" s="146"/>
-      <c r="Q65" s="146"/>
-      <c r="R65" s="146"/>
+      <c r="D65" s="114"/>
+      <c r="E65" s="114"/>
+      <c r="F65" s="114"/>
+      <c r="G65" s="114"/>
+      <c r="H65" s="114"/>
+      <c r="I65" s="114"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="114"/>
+      <c r="L65" s="114"/>
+      <c r="M65" s="114"/>
+      <c r="N65" s="114"/>
+      <c r="O65" s="114"/>
+      <c r="P65" s="114"/>
+      <c r="Q65" s="114"/>
+      <c r="R65" s="114"/>
       <c r="S65" s="44"/>
     </row>
     <row r="66" spans="2:19" ht="110.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="59"/>
-      <c r="C66" s="186" t="s">
+      <c r="C66" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="D66" s="187"/>
-      <c r="E66" s="187"/>
-      <c r="F66" s="187"/>
-      <c r="G66" s="187"/>
-      <c r="H66" s="187"/>
-      <c r="I66" s="187"/>
-      <c r="J66" s="187"/>
-      <c r="K66" s="187"/>
-      <c r="L66" s="187"/>
-      <c r="M66" s="187"/>
-      <c r="N66" s="187"/>
-      <c r="O66" s="187"/>
-      <c r="P66" s="187"/>
-      <c r="Q66" s="187"/>
-      <c r="R66" s="187"/>
+      <c r="D66" s="118"/>
+      <c r="E66" s="118"/>
+      <c r="F66" s="118"/>
+      <c r="G66" s="118"/>
+      <c r="H66" s="118"/>
+      <c r="I66" s="118"/>
+      <c r="J66" s="118"/>
+      <c r="K66" s="118"/>
+      <c r="L66" s="118"/>
+      <c r="M66" s="118"/>
+      <c r="N66" s="118"/>
+      <c r="O66" s="118"/>
+      <c r="P66" s="118"/>
+      <c r="Q66" s="118"/>
+      <c r="R66" s="118"/>
       <c r="S66" s="44"/>
     </row>
     <row r="67" spans="2:19" ht="10.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="59"/>
-      <c r="C67" s="145" t="s">
+      <c r="C67" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="146"/>
-      <c r="E67" s="146"/>
-      <c r="F67" s="146"/>
-      <c r="G67" s="146"/>
-      <c r="H67" s="146"/>
-      <c r="I67" s="146"/>
-      <c r="J67" s="146"/>
-      <c r="K67" s="146"/>
-      <c r="L67" s="146"/>
-      <c r="M67" s="146"/>
-      <c r="N67" s="146"/>
-      <c r="O67" s="146"/>
-      <c r="P67" s="146"/>
-      <c r="Q67" s="146"/>
-      <c r="R67" s="146"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="114"/>
+      <c r="F67" s="114"/>
+      <c r="G67" s="114"/>
+      <c r="H67" s="114"/>
+      <c r="I67" s="114"/>
+      <c r="J67" s="114"/>
+      <c r="K67" s="114"/>
+      <c r="L67" s="114"/>
+      <c r="M67" s="114"/>
+      <c r="N67" s="114"/>
+      <c r="O67" s="114"/>
+      <c r="P67" s="114"/>
+      <c r="Q67" s="114"/>
+      <c r="R67" s="114"/>
       <c r="S67" s="44"/>
     </row>
     <row r="68" spans="2:19" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="59"/>
-      <c r="C68" s="143" t="s">
+      <c r="C68" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="D68" s="144"/>
-      <c r="E68" s="144"/>
-      <c r="F68" s="144"/>
-      <c r="G68" s="144"/>
-      <c r="H68" s="144"/>
-      <c r="I68" s="144"/>
-      <c r="J68" s="144"/>
-      <c r="K68" s="144"/>
-      <c r="L68" s="144"/>
-      <c r="M68" s="144"/>
-      <c r="N68" s="144"/>
-      <c r="O68" s="144"/>
-      <c r="P68" s="144"/>
-      <c r="Q68" s="144"/>
-      <c r="R68" s="144"/>
+      <c r="D68" s="106"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="106"/>
+      <c r="G68" s="106"/>
+      <c r="H68" s="106"/>
+      <c r="I68" s="106"/>
+      <c r="J68" s="106"/>
+      <c r="K68" s="106"/>
+      <c r="L68" s="106"/>
+      <c r="M68" s="106"/>
+      <c r="N68" s="106"/>
+      <c r="O68" s="106"/>
+      <c r="P68" s="106"/>
+      <c r="Q68" s="106"/>
+      <c r="R68" s="106"/>
       <c r="S68" s="44"/>
     </row>
     <row r="69" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="59"/>
-      <c r="C69" s="155"/>
-      <c r="D69" s="156"/>
-      <c r="E69" s="156"/>
-      <c r="F69" s="156"/>
-      <c r="G69" s="156"/>
-      <c r="I69" s="156"/>
-      <c r="J69" s="156"/>
-      <c r="K69" s="156"/>
-      <c r="L69" s="156"/>
-      <c r="M69" s="156"/>
-      <c r="N69" s="156"/>
-      <c r="O69" s="156"/>
-      <c r="P69" s="156"/>
-      <c r="Q69" s="156"/>
-      <c r="R69" s="156"/>
+      <c r="C69" s="109"/>
+      <c r="D69" s="110"/>
+      <c r="E69" s="110"/>
+      <c r="F69" s="110"/>
+      <c r="G69" s="110"/>
+      <c r="I69" s="110"/>
+      <c r="J69" s="110"/>
+      <c r="K69" s="110"/>
+      <c r="L69" s="110"/>
+      <c r="M69" s="110"/>
+      <c r="N69" s="110"/>
+      <c r="O69" s="110"/>
+      <c r="P69" s="110"/>
+      <c r="Q69" s="110"/>
+      <c r="R69" s="110"/>
       <c r="S69" s="41"/>
     </row>
     <row r="70" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6957,89 +6953,89 @@
     </row>
     <row r="71" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="59"/>
-      <c r="C71" s="155" t="s">
+      <c r="C71" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="D71" s="156"/>
-      <c r="E71" s="156"/>
-      <c r="F71" s="156"/>
-      <c r="G71" s="156"/>
-      <c r="I71" s="156" t="s">
+      <c r="D71" s="110"/>
+      <c r="E71" s="110"/>
+      <c r="F71" s="110"/>
+      <c r="G71" s="110"/>
+      <c r="I71" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="J71" s="156"/>
-      <c r="K71" s="156"/>
-      <c r="L71" s="156"/>
-      <c r="M71" s="156"/>
-      <c r="N71" s="156"/>
-      <c r="O71" s="156"/>
-      <c r="P71" s="156"/>
-      <c r="Q71" s="156"/>
-      <c r="R71" s="156"/>
+      <c r="J71" s="110"/>
+      <c r="K71" s="110"/>
+      <c r="L71" s="110"/>
+      <c r="M71" s="110"/>
+      <c r="N71" s="110"/>
+      <c r="O71" s="110"/>
+      <c r="P71" s="110"/>
+      <c r="Q71" s="110"/>
+      <c r="R71" s="110"/>
       <c r="S71" s="41"/>
     </row>
     <row r="72" spans="2:19" ht="46.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B72" s="59"/>
-      <c r="C72" s="181" t="s">
+      <c r="C72" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="138"/>
-      <c r="E72" s="138"/>
-      <c r="F72" s="138"/>
-      <c r="G72" s="138"/>
-      <c r="H72" s="138"/>
-      <c r="I72" s="138"/>
-      <c r="J72" s="138"/>
-      <c r="K72" s="138"/>
-      <c r="L72" s="138"/>
-      <c r="M72" s="138"/>
-      <c r="N72" s="138"/>
-      <c r="O72" s="138"/>
-      <c r="P72" s="138"/>
-      <c r="Q72" s="138"/>
-      <c r="R72" s="138"/>
+      <c r="D72" s="104"/>
+      <c r="E72" s="104"/>
+      <c r="F72" s="104"/>
+      <c r="G72" s="104"/>
+      <c r="H72" s="104"/>
+      <c r="I72" s="104"/>
+      <c r="J72" s="104"/>
+      <c r="K72" s="104"/>
+      <c r="L72" s="104"/>
+      <c r="M72" s="104"/>
+      <c r="N72" s="104"/>
+      <c r="O72" s="104"/>
+      <c r="P72" s="104"/>
+      <c r="Q72" s="104"/>
+      <c r="R72" s="104"/>
       <c r="S72" s="41"/>
     </row>
     <row r="73" spans="2:19" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="59"/>
-      <c r="C73" s="157" t="s">
+      <c r="C73" s="160" t="s">
         <v>130</v>
       </c>
-      <c r="D73" s="157"/>
-      <c r="E73" s="157"/>
-      <c r="F73" s="157"/>
-      <c r="G73" s="157"/>
-      <c r="H73" s="157"/>
-      <c r="I73" s="157"/>
-      <c r="J73" s="157"/>
-      <c r="K73" s="157"/>
-      <c r="L73" s="157"/>
-      <c r="M73" s="157"/>
-      <c r="N73" s="157"/>
-      <c r="O73" s="157"/>
-      <c r="P73" s="157"/>
-      <c r="Q73" s="157"/>
-      <c r="R73" s="157"/>
+      <c r="D73" s="160"/>
+      <c r="E73" s="160"/>
+      <c r="F73" s="160"/>
+      <c r="G73" s="160"/>
+      <c r="H73" s="160"/>
+      <c r="I73" s="160"/>
+      <c r="J73" s="160"/>
+      <c r="K73" s="160"/>
+      <c r="L73" s="160"/>
+      <c r="M73" s="160"/>
+      <c r="N73" s="160"/>
+      <c r="O73" s="160"/>
+      <c r="P73" s="160"/>
+      <c r="Q73" s="160"/>
+      <c r="R73" s="160"/>
       <c r="S73" s="41"/>
     </row>
     <row r="74" spans="2:19" ht="62.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="59"/>
-      <c r="C74" s="158"/>
-      <c r="D74" s="158"/>
-      <c r="E74" s="158"/>
-      <c r="F74" s="158"/>
-      <c r="G74" s="158"/>
-      <c r="H74" s="158"/>
-      <c r="I74" s="158"/>
-      <c r="J74" s="158"/>
-      <c r="K74" s="158"/>
-      <c r="L74" s="158"/>
-      <c r="M74" s="158"/>
-      <c r="N74" s="158"/>
-      <c r="O74" s="158"/>
-      <c r="P74" s="158"/>
-      <c r="Q74" s="158"/>
-      <c r="R74" s="158"/>
+      <c r="C74" s="161"/>
+      <c r="D74" s="161"/>
+      <c r="E74" s="161"/>
+      <c r="F74" s="161"/>
+      <c r="G74" s="161"/>
+      <c r="H74" s="161"/>
+      <c r="I74" s="161"/>
+      <c r="J74" s="161"/>
+      <c r="K74" s="161"/>
+      <c r="L74" s="161"/>
+      <c r="M74" s="161"/>
+      <c r="N74" s="161"/>
+      <c r="O74" s="161"/>
+      <c r="P74" s="161"/>
+      <c r="Q74" s="161"/>
+      <c r="R74" s="161"/>
       <c r="S74" s="41"/>
     </row>
     <row r="75" spans="2:19" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7064,29 +7060,107 @@
     </row>
     <row r="76" spans="2:19" ht="22.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="45"/>
-      <c r="C76" s="138" t="s">
+      <c r="C76" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="D76" s="138"/>
-      <c r="E76" s="138"/>
-      <c r="F76" s="138"/>
-      <c r="G76" s="138"/>
-      <c r="H76" s="138"/>
-      <c r="I76" s="138"/>
-      <c r="J76" s="138"/>
-      <c r="K76" s="138"/>
-      <c r="L76" s="138"/>
-      <c r="M76" s="138"/>
-      <c r="N76" s="138"/>
-      <c r="O76" s="138"/>
-      <c r="P76" s="138"/>
-      <c r="Q76" s="138"/>
-      <c r="R76" s="138"/>
+      <c r="D76" s="104"/>
+      <c r="E76" s="104"/>
+      <c r="F76" s="104"/>
+      <c r="G76" s="104"/>
+      <c r="H76" s="104"/>
+      <c r="I76" s="104"/>
+      <c r="J76" s="104"/>
+      <c r="K76" s="104"/>
+      <c r="L76" s="104"/>
+      <c r="M76" s="104"/>
+      <c r="N76" s="104"/>
+      <c r="O76" s="104"/>
+      <c r="P76" s="104"/>
+      <c r="Q76" s="104"/>
+      <c r="R76" s="104"/>
       <c r="S76" s="46"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="102">
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="L18:R18"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="L20:R20"/>
+    <mergeCell ref="L19:R19"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="L9:R9"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J11:Q11"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="C24:R24"/>
+    <mergeCell ref="C42:R42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C34:R34"/>
+    <mergeCell ref="C37:R37"/>
+    <mergeCell ref="C40:J40"/>
+    <mergeCell ref="K40:R40"/>
+    <mergeCell ref="C41:R41"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C33:R33"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="O30:O31"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="C76:R76"/>
+    <mergeCell ref="C44:R44"/>
+    <mergeCell ref="C45:R45"/>
+    <mergeCell ref="C46:R46"/>
+    <mergeCell ref="C47:R47"/>
+    <mergeCell ref="C57:R57"/>
+    <mergeCell ref="C58:R58"/>
+    <mergeCell ref="C55:R55"/>
+    <mergeCell ref="C60:R60"/>
+    <mergeCell ref="C52:R52"/>
+    <mergeCell ref="C53:R53"/>
+    <mergeCell ref="C48:R48"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="I71:R71"/>
+    <mergeCell ref="C59:R59"/>
+    <mergeCell ref="C73:R74"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="C3:L3"/>
+    <mergeCell ref="C4:R4"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C5:R5"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="C39:R39"/>
+    <mergeCell ref="C7:R7"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="C16:R16"/>
+    <mergeCell ref="C12:R12"/>
+    <mergeCell ref="C10:R10"/>
+    <mergeCell ref="L14:R14"/>
+    <mergeCell ref="L13:R13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="M17:R17"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="D15:R15"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="C21:R21"/>
+    <mergeCell ref="C23:R23"/>
+    <mergeCell ref="M32:R32"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="C36:R36"/>
@@ -7111,88 +7185,11 @@
     <mergeCell ref="C25:L26"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="M27:M28"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="C3:L3"/>
-    <mergeCell ref="C4:R4"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C5:R5"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="C39:R39"/>
-    <mergeCell ref="C7:R7"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="C16:R16"/>
-    <mergeCell ref="C12:R12"/>
-    <mergeCell ref="C10:R10"/>
-    <mergeCell ref="L14:R14"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="M17:R17"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="D15:R15"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="C21:R21"/>
-    <mergeCell ref="C23:R23"/>
-    <mergeCell ref="M32:R32"/>
-    <mergeCell ref="C76:R76"/>
-    <mergeCell ref="C44:R44"/>
-    <mergeCell ref="C45:R45"/>
-    <mergeCell ref="C46:R46"/>
-    <mergeCell ref="C47:R47"/>
-    <mergeCell ref="C57:R57"/>
-    <mergeCell ref="C58:R58"/>
-    <mergeCell ref="C55:R55"/>
-    <mergeCell ref="C60:R60"/>
-    <mergeCell ref="C52:R52"/>
-    <mergeCell ref="C53:R53"/>
-    <mergeCell ref="C48:R48"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="I71:R71"/>
-    <mergeCell ref="C59:R59"/>
-    <mergeCell ref="C73:R74"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="R30:R31"/>
-    <mergeCell ref="Q30:Q31"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="O30:O31"/>
-    <mergeCell ref="N30:N31"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="L18:R18"/>
-    <mergeCell ref="D19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="L20:R20"/>
-    <mergeCell ref="L19:R19"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:R6"/>
-    <mergeCell ref="L9:R9"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J11:Q11"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="C24:R24"/>
-    <mergeCell ref="C42:R42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C34:R34"/>
-    <mergeCell ref="C37:R37"/>
-    <mergeCell ref="C40:J40"/>
-    <mergeCell ref="K40:R40"/>
-    <mergeCell ref="C41:R41"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C33:R33"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
-  <pageMargins left="0.43" right="0.26" top="0.45" bottom="0.46" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="62" orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30000000000000004" right="0.30000000000000004" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup scale="67" fitToHeight="2" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -7606,62 +7603,62 @@
         <v xml:space="preserve">Sexo: </v>
       </c>
       <c r="C1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -7693,53 +7690,53 @@
   <sheetData>
     <row r="1" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:15" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D2" s="228" t="s">
+      <c r="D2" s="201" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230"/>
-      <c r="I2" s="225" t="s">
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="227"/>
+      <c r="J2" s="199"/>
+      <c r="K2" s="199"/>
+      <c r="L2" s="200"/>
       <c r="M2" s="19"/>
       <c r="N2" s="19"/>
       <c r="O2" s="20"/>
     </row>
     <row r="3" spans="3:15" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D3" s="231"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="232"/>
-      <c r="H3" s="233"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="206"/>
       <c r="I3" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="221" t="s">
+      <c r="J3" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="K3" s="221"/>
-      <c r="L3" s="222"/>
+      <c r="K3" s="194"/>
+      <c r="L3" s="195"/>
       <c r="O3" s="21"/>
     </row>
     <row r="4" spans="3:15" ht="13.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="234"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="236"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="209"/>
       <c r="I4" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="223" t="s">
+      <c r="J4" s="196" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="223"/>
-      <c r="L4" s="224"/>
+      <c r="K4" s="196"/>
+      <c r="L4" s="197"/>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="23"/>
@@ -7760,20 +7757,20 @@
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6" s="14"/>
-      <c r="D6" s="253" t="s">
+      <c r="D6" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="253"/>
-      <c r="F6" s="253"/>
-      <c r="G6" s="253"/>
-      <c r="H6" s="253"/>
-      <c r="I6" s="253"/>
-      <c r="J6" s="253"/>
-      <c r="K6" s="253"/>
-      <c r="L6" s="253"/>
-      <c r="M6" s="253"/>
-      <c r="N6" s="253"/>
-      <c r="O6" s="254"/>
+      <c r="E6" s="228"/>
+      <c r="F6" s="228"/>
+      <c r="G6" s="228"/>
+      <c r="H6" s="228"/>
+      <c r="I6" s="228"/>
+      <c r="J6" s="228"/>
+      <c r="K6" s="228"/>
+      <c r="L6" s="228"/>
+      <c r="M6" s="228"/>
+      <c r="N6" s="228"/>
+      <c r="O6" s="229"/>
     </row>
     <row r="7" spans="3:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="14"/>
@@ -7783,15 +7780,15 @@
       <c r="E7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="212">
+      <c r="F7" s="237">
         <v>1121310100012</v>
       </c>
-      <c r="G7" s="213"/>
-      <c r="H7" s="214"/>
-      <c r="I7" s="211" t="s">
+      <c r="G7" s="238"/>
+      <c r="H7" s="239"/>
+      <c r="I7" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="206"/>
+      <c r="J7" s="211"/>
       <c r="K7" s="35" t="s">
         <v>76</v>
       </c>
@@ -7814,15 +7811,15 @@
       <c r="E8" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="212">
+      <c r="F8" s="237">
         <v>1121310100012</v>
       </c>
-      <c r="G8" s="213"/>
-      <c r="H8" s="214"/>
-      <c r="I8" s="211" t="s">
+      <c r="G8" s="238"/>
+      <c r="H8" s="239"/>
+      <c r="I8" s="236" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="206"/>
+      <c r="J8" s="211"/>
       <c r="K8" s="35" t="s">
         <v>76</v>
       </c>
@@ -7844,61 +7841,61 @@
       <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="209" t="s">
+      <c r="E9" s="240" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="210"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="241"/>
       <c r="I9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="209" t="s">
+      <c r="K9" s="240" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="209"/>
-      <c r="M9" s="209"/>
-      <c r="N9" s="209"/>
-      <c r="O9" s="210"/>
+      <c r="L9" s="240"/>
+      <c r="M9" s="240"/>
+      <c r="N9" s="240"/>
+      <c r="O9" s="241"/>
     </row>
     <row r="10" spans="3:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="14"/>
-      <c r="D10" s="253" t="s">
+      <c r="D10" s="228" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="253"/>
-      <c r="F10" s="253"/>
-      <c r="G10" s="253"/>
-      <c r="H10" s="253"/>
-      <c r="I10" s="253"/>
-      <c r="J10" s="253"/>
-      <c r="K10" s="253"/>
-      <c r="L10" s="253"/>
-      <c r="M10" s="253"/>
-      <c r="N10" s="253"/>
-      <c r="O10" s="254"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="228"/>
+      <c r="I10" s="228"/>
+      <c r="J10" s="228"/>
+      <c r="K10" s="228"/>
+      <c r="L10" s="228"/>
+      <c r="M10" s="228"/>
+      <c r="N10" s="228"/>
+      <c r="O10" s="229"/>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C11" s="14"/>
       <c r="D11" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="252"/>
+      <c r="E11" s="226"/>
+      <c r="F11" s="226"/>
+      <c r="G11" s="226"/>
+      <c r="H11" s="227"/>
       <c r="I11" s="11" t="s">
         <v>15</v>
       </c>
       <c r="J11" s="11"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="250" t="s">
+      <c r="K11" s="214"/>
+      <c r="L11" s="214"/>
+      <c r="M11" s="225" t="s">
         <v>83</v>
       </c>
-      <c r="N11" s="251"/>
-      <c r="O11" s="252"/>
+      <c r="N11" s="226"/>
+      <c r="O11" s="227"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
@@ -7975,75 +7972,75 @@
     </row>
     <row r="16" spans="3:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="14"/>
-      <c r="D16" s="237" t="s">
+      <c r="D16" s="212" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="237"/>
-      <c r="J16" s="237"/>
-      <c r="K16" s="237"/>
-      <c r="L16" s="237"/>
-      <c r="M16" s="237"/>
-      <c r="N16" s="237"/>
-      <c r="O16" s="238"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="212"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="212"/>
+      <c r="L16" s="212"/>
+      <c r="M16" s="212"/>
+      <c r="N16" s="212"/>
+      <c r="O16" s="213"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C17" s="14"/>
-      <c r="D17" s="239" t="s">
+      <c r="D17" s="214" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="239"/>
-      <c r="F17" s="239"/>
-      <c r="G17" s="239"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="241" t="s">
+      <c r="E17" s="214"/>
+      <c r="F17" s="214"/>
+      <c r="G17" s="214"/>
+      <c r="H17" s="215"/>
+      <c r="I17" s="216" t="s">
         <v>92</v>
       </c>
-      <c r="J17" s="239"/>
-      <c r="K17" s="239"/>
-      <c r="L17" s="239"/>
-      <c r="M17" s="239"/>
-      <c r="N17" s="239"/>
-      <c r="O17" s="240"/>
+      <c r="J17" s="214"/>
+      <c r="K17" s="214"/>
+      <c r="L17" s="214"/>
+      <c r="M17" s="214"/>
+      <c r="N17" s="214"/>
+      <c r="O17" s="215"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C18" s="14"/>
-      <c r="D18" s="248" t="s">
+      <c r="D18" s="223" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="249"/>
-      <c r="I18" s="242" t="s">
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="224"/>
+      <c r="I18" s="217" t="s">
         <v>94</v>
       </c>
-      <c r="J18" s="243"/>
-      <c r="K18" s="243"/>
-      <c r="L18" s="243"/>
-      <c r="M18" s="243"/>
-      <c r="N18" s="243"/>
-      <c r="O18" s="244"/>
+      <c r="J18" s="218"/>
+      <c r="K18" s="218"/>
+      <c r="L18" s="218"/>
+      <c r="M18" s="218"/>
+      <c r="N18" s="218"/>
+      <c r="O18" s="219"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C19" s="14"/>
-      <c r="D19" s="248" t="s">
+      <c r="D19" s="223" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="248"/>
-      <c r="F19" s="248"/>
-      <c r="G19" s="248"/>
-      <c r="H19" s="249"/>
-      <c r="I19" s="245"/>
-      <c r="J19" s="246"/>
-      <c r="K19" s="246"/>
-      <c r="L19" s="246"/>
-      <c r="M19" s="246"/>
-      <c r="N19" s="246"/>
-      <c r="O19" s="247"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="223"/>
+      <c r="G19" s="223"/>
+      <c r="H19" s="224"/>
+      <c r="I19" s="220"/>
+      <c r="J19" s="221"/>
+      <c r="K19" s="221"/>
+      <c r="L19" s="221"/>
+      <c r="M19" s="221"/>
+      <c r="N19" s="221"/>
+      <c r="O19" s="222"/>
     </row>
     <row r="20" spans="3:20" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="15"/>
@@ -8060,64 +8057,64 @@
       <c r="O20" s="15"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="D21" s="203" t="s">
+      <c r="D21" s="251" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="203"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="203"/>
-      <c r="H21" s="203"/>
-      <c r="I21" s="203"/>
-      <c r="J21" s="203"/>
-      <c r="K21" s="203"/>
-      <c r="L21" s="203"/>
-      <c r="M21" s="203"/>
-      <c r="N21" s="203"/>
-      <c r="O21" s="204"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
+      <c r="M21" s="251"/>
+      <c r="N21" s="251"/>
+      <c r="O21" s="252"/>
     </row>
     <row r="22" spans="3:20" ht="24" x14ac:dyDescent="0.3">
       <c r="D22" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="205" t="s">
+      <c r="E22" s="210" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="207"/>
-      <c r="G22" s="208"/>
-      <c r="H22" s="205" t="s">
+      <c r="F22" s="253"/>
+      <c r="G22" s="254"/>
+      <c r="H22" s="210" t="s">
         <v>99</v>
       </c>
-      <c r="I22" s="207"/>
-      <c r="J22" s="207"/>
-      <c r="K22" s="208"/>
-      <c r="L22" s="205" t="s">
+      <c r="I22" s="253"/>
+      <c r="J22" s="253"/>
+      <c r="K22" s="254"/>
+      <c r="L22" s="210" t="s">
         <v>100</v>
       </c>
-      <c r="M22" s="208"/>
-      <c r="N22" s="205" t="s">
+      <c r="M22" s="254"/>
+      <c r="N22" s="210" t="s">
         <v>101</v>
       </c>
-      <c r="O22" s="206"/>
+      <c r="O22" s="211"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D23" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="200">
+      <c r="E23" s="248">
         <v>150000</v>
       </c>
-      <c r="F23" s="201"/>
-      <c r="G23" s="202"/>
-      <c r="H23" s="197" t="s">
+      <c r="F23" s="249"/>
+      <c r="G23" s="250"/>
+      <c r="H23" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="198"/>
-      <c r="J23" s="198"/>
-      <c r="K23" s="199"/>
-      <c r="L23" s="200">
+      <c r="I23" s="246"/>
+      <c r="J23" s="246"/>
+      <c r="K23" s="247"/>
+      <c r="L23" s="248">
         <v>6000</v>
       </c>
-      <c r="M23" s="202"/>
+      <c r="M23" s="250"/>
       <c r="N23" s="16"/>
       <c r="O23" s="17"/>
       <c r="P23" s="34"/>
@@ -8129,21 +8126,21 @@
       <c r="D24" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="200">
+      <c r="E24" s="248">
         <v>500000</v>
       </c>
-      <c r="F24" s="201"/>
-      <c r="G24" s="202"/>
-      <c r="H24" s="197" t="s">
+      <c r="F24" s="249"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="198"/>
-      <c r="J24" s="198"/>
-      <c r="K24" s="199"/>
-      <c r="L24" s="200">
+      <c r="I24" s="246"/>
+      <c r="J24" s="246"/>
+      <c r="K24" s="247"/>
+      <c r="L24" s="248">
         <v>17500</v>
       </c>
-      <c r="M24" s="202"/>
+      <c r="M24" s="250"/>
       <c r="N24" s="16"/>
       <c r="O24" s="17"/>
       <c r="P24" s="34"/>
@@ -8155,21 +8152,21 @@
       <c r="D25" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="200">
+      <c r="E25" s="248">
         <v>500000</v>
       </c>
-      <c r="F25" s="201"/>
-      <c r="G25" s="202"/>
-      <c r="H25" s="197" t="s">
+      <c r="F25" s="249"/>
+      <c r="G25" s="250"/>
+      <c r="H25" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I25" s="198"/>
-      <c r="J25" s="198"/>
-      <c r="K25" s="199"/>
-      <c r="L25" s="200">
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="247"/>
+      <c r="L25" s="248">
         <v>21500</v>
       </c>
-      <c r="M25" s="202"/>
+      <c r="M25" s="250"/>
       <c r="N25" s="26"/>
       <c r="O25" s="27"/>
       <c r="P25" s="34"/>
@@ -8181,21 +8178,21 @@
       <c r="D26" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="200">
+      <c r="E26" s="248">
         <v>625000</v>
       </c>
-      <c r="F26" s="201"/>
-      <c r="G26" s="202"/>
-      <c r="H26" s="197" t="s">
+      <c r="F26" s="249"/>
+      <c r="G26" s="250"/>
+      <c r="H26" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="198"/>
-      <c r="J26" s="198"/>
-      <c r="K26" s="199"/>
-      <c r="L26" s="200">
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="247"/>
+      <c r="L26" s="248">
         <v>27500</v>
       </c>
-      <c r="M26" s="202"/>
+      <c r="M26" s="250"/>
       <c r="N26" s="16"/>
       <c r="O26" s="17"/>
       <c r="Q26" s="38">
@@ -8206,21 +8203,21 @@
       <c r="D27" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="200">
+      <c r="E27" s="248">
         <v>625000</v>
       </c>
-      <c r="F27" s="201"/>
-      <c r="G27" s="202"/>
-      <c r="H27" s="197" t="s">
+      <c r="F27" s="249"/>
+      <c r="G27" s="250"/>
+      <c r="H27" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I27" s="198"/>
-      <c r="J27" s="198"/>
-      <c r="K27" s="199"/>
-      <c r="L27" s="200">
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="247"/>
+      <c r="L27" s="248">
         <v>31500</v>
       </c>
-      <c r="M27" s="202"/>
+      <c r="M27" s="250"/>
       <c r="N27" s="5"/>
       <c r="O27" s="6"/>
       <c r="Q27" s="38">
@@ -8231,86 +8228,86 @@
       <c r="D28" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="200">
+      <c r="E28" s="248">
         <v>625000</v>
       </c>
-      <c r="F28" s="201"/>
-      <c r="G28" s="202"/>
-      <c r="H28" s="197" t="s">
+      <c r="F28" s="249"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I28" s="198"/>
-      <c r="J28" s="198"/>
-      <c r="K28" s="199"/>
-      <c r="L28" s="200">
+      <c r="I28" s="246"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="247"/>
+      <c r="L28" s="248">
         <v>35000</v>
       </c>
-      <c r="M28" s="202"/>
+      <c r="M28" s="250"/>
       <c r="N28" s="5"/>
       <c r="O28" s="6"/>
       <c r="Q28" s="38"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C29" s="14"/>
-      <c r="D29" s="203" t="s">
+      <c r="D29" s="251" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="203"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="203"/>
-      <c r="H29" s="203"/>
-      <c r="I29" s="203"/>
-      <c r="J29" s="203"/>
-      <c r="K29" s="203"/>
-      <c r="L29" s="203"/>
-      <c r="M29" s="203"/>
-      <c r="N29" s="203"/>
-      <c r="O29" s="204"/>
+      <c r="E29" s="251"/>
+      <c r="F29" s="251"/>
+      <c r="G29" s="251"/>
+      <c r="H29" s="251"/>
+      <c r="I29" s="251"/>
+      <c r="J29" s="251"/>
+      <c r="K29" s="251"/>
+      <c r="L29" s="251"/>
+      <c r="M29" s="251"/>
+      <c r="N29" s="251"/>
+      <c r="O29" s="252"/>
       <c r="Q29" s="38"/>
     </row>
     <row r="30" spans="3:20" ht="24" x14ac:dyDescent="0.3">
       <c r="D30" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="E30" s="205" t="s">
+      <c r="E30" s="210" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="207"/>
-      <c r="G30" s="208"/>
-      <c r="H30" s="205" t="s">
+      <c r="F30" s="253"/>
+      <c r="G30" s="254"/>
+      <c r="H30" s="210" t="s">
         <v>99</v>
       </c>
-      <c r="I30" s="207"/>
-      <c r="J30" s="207"/>
-      <c r="K30" s="208"/>
-      <c r="L30" s="205" t="s">
+      <c r="I30" s="253"/>
+      <c r="J30" s="253"/>
+      <c r="K30" s="254"/>
+      <c r="L30" s="210" t="s">
         <v>100</v>
       </c>
-      <c r="M30" s="208"/>
-      <c r="N30" s="205" t="s">
+      <c r="M30" s="254"/>
+      <c r="N30" s="210" t="s">
         <v>101</v>
       </c>
-      <c r="O30" s="206"/>
+      <c r="O30" s="211"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D31" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="194">
+      <c r="E31" s="242">
         <v>300</v>
       </c>
-      <c r="F31" s="195"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="197" t="s">
+      <c r="F31" s="244"/>
+      <c r="G31" s="243"/>
+      <c r="H31" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="198"/>
-      <c r="J31" s="198"/>
-      <c r="K31" s="199"/>
-      <c r="L31" s="194">
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="247"/>
+      <c r="L31" s="242">
         <v>12</v>
       </c>
-      <c r="M31" s="196"/>
+      <c r="M31" s="243"/>
       <c r="N31" s="16"/>
       <c r="O31" s="17"/>
       <c r="P31" s="34"/>
@@ -8321,21 +8318,21 @@
       <c r="D32" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="194">
+      <c r="E32" s="242">
         <v>1000</v>
       </c>
-      <c r="F32" s="195"/>
-      <c r="G32" s="196"/>
-      <c r="H32" s="197" t="s">
+      <c r="F32" s="244"/>
+      <c r="G32" s="243"/>
+      <c r="H32" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="198"/>
-      <c r="J32" s="198"/>
-      <c r="K32" s="199"/>
-      <c r="L32" s="194">
+      <c r="I32" s="246"/>
+      <c r="J32" s="246"/>
+      <c r="K32" s="247"/>
+      <c r="L32" s="242">
         <v>35</v>
       </c>
-      <c r="M32" s="196"/>
+      <c r="M32" s="243"/>
       <c r="N32" s="16"/>
       <c r="O32" s="17"/>
       <c r="S32" s="18"/>
@@ -8345,21 +8342,21 @@
       <c r="D33" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="E33" s="194">
+      <c r="E33" s="242">
         <v>1000</v>
       </c>
-      <c r="F33" s="195"/>
-      <c r="G33" s="196"/>
-      <c r="H33" s="197" t="s">
+      <c r="F33" s="244"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I33" s="198"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="199"/>
-      <c r="L33" s="194">
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="247"/>
+      <c r="L33" s="242">
         <v>43</v>
       </c>
-      <c r="M33" s="196"/>
+      <c r="M33" s="243"/>
       <c r="N33" s="26"/>
       <c r="O33" s="27"/>
       <c r="S33" s="18"/>
@@ -8369,21 +8366,21 @@
       <c r="D34" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="194">
+      <c r="E34" s="242">
         <v>1250</v>
       </c>
-      <c r="F34" s="195"/>
-      <c r="G34" s="196"/>
-      <c r="H34" s="197" t="s">
+      <c r="F34" s="244"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I34" s="198"/>
-      <c r="J34" s="198"/>
-      <c r="K34" s="199"/>
-      <c r="L34" s="194">
+      <c r="I34" s="246"/>
+      <c r="J34" s="246"/>
+      <c r="K34" s="247"/>
+      <c r="L34" s="242">
         <v>55</v>
       </c>
-      <c r="M34" s="196"/>
+      <c r="M34" s="243"/>
       <c r="N34" s="16"/>
       <c r="O34" s="17"/>
       <c r="S34" s="18"/>
@@ -8393,21 +8390,21 @@
       <c r="D35" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="E35" s="194">
+      <c r="E35" s="242">
         <v>1250</v>
       </c>
-      <c r="F35" s="195"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="197" t="s">
+      <c r="F35" s="244"/>
+      <c r="G35" s="243"/>
+      <c r="H35" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I35" s="198"/>
-      <c r="J35" s="198"/>
-      <c r="K35" s="199"/>
-      <c r="L35" s="194">
+      <c r="I35" s="246"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="247"/>
+      <c r="L35" s="242">
         <v>63</v>
       </c>
-      <c r="M35" s="196"/>
+      <c r="M35" s="243"/>
       <c r="N35" s="5"/>
       <c r="O35" s="6"/>
     </row>
@@ -8415,55 +8412,55 @@
       <c r="D36" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="194">
+      <c r="E36" s="242">
         <v>1250</v>
       </c>
-      <c r="F36" s="195"/>
-      <c r="G36" s="196"/>
-      <c r="H36" s="197" t="s">
+      <c r="F36" s="244"/>
+      <c r="G36" s="243"/>
+      <c r="H36" s="245" t="s">
         <v>103</v>
       </c>
-      <c r="I36" s="198"/>
-      <c r="J36" s="198"/>
-      <c r="K36" s="199"/>
-      <c r="L36" s="194">
+      <c r="I36" s="246"/>
+      <c r="J36" s="246"/>
+      <c r="K36" s="247"/>
+      <c r="L36" s="242">
         <v>70</v>
       </c>
-      <c r="M36" s="196"/>
+      <c r="M36" s="243"/>
       <c r="N36" s="5"/>
       <c r="O36" s="6"/>
     </row>
     <row r="37" spans="4:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="218" t="s">
+      <c r="D37" s="233" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="218"/>
-      <c r="F37" s="218"/>
-      <c r="G37" s="218"/>
-      <c r="H37" s="218"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="218"/>
-      <c r="K37" s="218"/>
-      <c r="L37" s="218"/>
-      <c r="M37" s="218"/>
-      <c r="N37" s="218"/>
-      <c r="O37" s="218"/>
+      <c r="E37" s="233"/>
+      <c r="F37" s="233"/>
+      <c r="G37" s="233"/>
+      <c r="H37" s="233"/>
+      <c r="I37" s="233"/>
+      <c r="J37" s="233"/>
+      <c r="K37" s="233"/>
+      <c r="L37" s="233"/>
+      <c r="M37" s="233"/>
+      <c r="N37" s="233"/>
+      <c r="O37" s="233"/>
     </row>
     <row r="38" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="218" t="s">
+      <c r="D38" s="233" t="s">
         <v>117</v>
       </c>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="218"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="218"/>
-      <c r="K38" s="218"/>
-      <c r="L38" s="218"/>
-      <c r="M38" s="218"/>
-      <c r="N38" s="218"/>
-      <c r="O38" s="218"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="233"/>
+      <c r="H38" s="233"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="233"/>
+      <c r="N38" s="233"/>
+      <c r="O38" s="233"/>
     </row>
     <row r="39" spans="4:20" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D39" s="2"/>
@@ -8480,52 +8477,52 @@
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="219" t="s">
+      <c r="D40" s="234" t="s">
         <v>118</v>
       </c>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="219"/>
-      <c r="I40" s="219"/>
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
-      <c r="M40" s="219"/>
-      <c r="N40" s="219"/>
-      <c r="O40" s="219"/>
+      <c r="E40" s="234"/>
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="234"/>
+      <c r="O40" s="234"/>
     </row>
     <row r="41" spans="4:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="219" t="s">
+      <c r="D41" s="234" t="s">
         <v>119</v>
       </c>
-      <c r="E41" s="219"/>
-      <c r="F41" s="219"/>
-      <c r="G41" s="219"/>
-      <c r="H41" s="219"/>
-      <c r="I41" s="219"/>
-      <c r="J41" s="219"/>
-      <c r="K41" s="219"/>
-      <c r="L41" s="219"/>
-      <c r="M41" s="219"/>
-      <c r="N41" s="219"/>
-      <c r="O41" s="219"/>
+      <c r="E41" s="234"/>
+      <c r="F41" s="234"/>
+      <c r="G41" s="234"/>
+      <c r="H41" s="234"/>
+      <c r="I41" s="234"/>
+      <c r="J41" s="234"/>
+      <c r="K41" s="234"/>
+      <c r="L41" s="234"/>
+      <c r="M41" s="234"/>
+      <c r="N41" s="234"/>
+      <c r="O41" s="234"/>
     </row>
     <row r="42" spans="4:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="219" t="s">
+      <c r="D42" s="234" t="s">
         <v>120</v>
       </c>
-      <c r="E42" s="219"/>
-      <c r="F42" s="219"/>
-      <c r="G42" s="219"/>
-      <c r="H42" s="219"/>
-      <c r="I42" s="219"/>
-      <c r="J42" s="219"/>
-      <c r="K42" s="219"/>
-      <c r="L42" s="219"/>
-      <c r="M42" s="219"/>
-      <c r="N42" s="219"/>
-      <c r="O42" s="219"/>
+      <c r="E42" s="234"/>
+      <c r="F42" s="234"/>
+      <c r="G42" s="234"/>
+      <c r="H42" s="234"/>
+      <c r="I42" s="234"/>
+      <c r="J42" s="234"/>
+      <c r="K42" s="234"/>
+      <c r="L42" s="234"/>
+      <c r="M42" s="234"/>
+      <c r="N42" s="234"/>
+      <c r="O42" s="234"/>
     </row>
     <row r="43" spans="4:20" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="44" spans="4:20" s="32" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
@@ -8536,64 +8533,124 @@
     </row>
     <row r="45" spans="4:20" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" s="1"/>
-      <c r="M45" s="220" t="s">
+      <c r="M45" s="235" t="s">
         <v>122</v>
       </c>
-      <c r="N45" s="220"/>
-      <c r="O45" s="220"/>
+      <c r="N45" s="235"/>
+      <c r="O45" s="235"/>
     </row>
     <row r="46" spans="4:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="4:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D47" s="215" t="s">
+      <c r="D47" s="230" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="215"/>
-      <c r="F47" s="215"/>
-      <c r="G47" s="215"/>
-      <c r="H47" s="215"/>
-      <c r="I47" s="215"/>
-      <c r="J47" s="215"/>
-      <c r="K47" s="215"/>
-      <c r="L47" s="215"/>
-      <c r="M47" s="215"/>
-      <c r="N47" s="215"/>
-      <c r="O47" s="215"/>
+      <c r="E47" s="230"/>
+      <c r="F47" s="230"/>
+      <c r="G47" s="230"/>
+      <c r="H47" s="230"/>
+      <c r="I47" s="230"/>
+      <c r="J47" s="230"/>
+      <c r="K47" s="230"/>
+      <c r="L47" s="230"/>
+      <c r="M47" s="230"/>
+      <c r="N47" s="230"/>
+      <c r="O47" s="230"/>
     </row>
     <row r="48" spans="4:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D48" s="216" t="s">
+      <c r="D48" s="231" t="s">
         <v>124</v>
       </c>
-      <c r="E48" s="216"/>
-      <c r="F48" s="216"/>
-      <c r="G48" s="216"/>
-      <c r="H48" s="216"/>
-      <c r="I48" s="216"/>
-      <c r="J48" s="216"/>
-      <c r="K48" s="216"/>
-      <c r="L48" s="216"/>
-      <c r="M48" s="216"/>
-      <c r="N48" s="216"/>
-      <c r="O48" s="216"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="231"/>
+      <c r="L48" s="231"/>
+      <c r="M48" s="231"/>
+      <c r="N48" s="231"/>
+      <c r="O48" s="231"/>
     </row>
     <row r="49" spans="4:15" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" spans="4:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D50" s="217" t="s">
+      <c r="D50" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="E50" s="217"/>
-      <c r="F50" s="217"/>
-      <c r="G50" s="217"/>
-      <c r="H50" s="217"/>
-      <c r="I50" s="217"/>
-      <c r="J50" s="217"/>
-      <c r="K50" s="217"/>
-      <c r="L50" s="217"/>
-      <c r="M50" s="217"/>
-      <c r="N50" s="217"/>
-      <c r="O50" s="217"/>
+      <c r="E50" s="232"/>
+      <c r="F50" s="232"/>
+      <c r="G50" s="232"/>
+      <c r="H50" s="232"/>
+      <c r="I50" s="232"/>
+      <c r="J50" s="232"/>
+      <c r="K50" s="232"/>
+      <c r="L50" s="232"/>
+      <c r="M50" s="232"/>
+      <c r="N50" s="232"/>
+      <c r="O50" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="D29:O29"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="D21:O21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="K9:O9"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="D47:O47"/>
+    <mergeCell ref="D48:O48"/>
+    <mergeCell ref="D50:O50"/>
+    <mergeCell ref="D37:O37"/>
+    <mergeCell ref="D38:O38"/>
+    <mergeCell ref="D40:O40"/>
+    <mergeCell ref="D41:O41"/>
+    <mergeCell ref="D42:O42"/>
+    <mergeCell ref="M45:O45"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="I2:L2"/>
@@ -8610,66 +8667,6 @@
     <mergeCell ref="D6:O6"/>
     <mergeCell ref="E11:H11"/>
     <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D47:O47"/>
-    <mergeCell ref="D48:O48"/>
-    <mergeCell ref="D50:O50"/>
-    <mergeCell ref="D37:O37"/>
-    <mergeCell ref="D38:O38"/>
-    <mergeCell ref="D40:O40"/>
-    <mergeCell ref="D41:O41"/>
-    <mergeCell ref="D42:O42"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="K9:O9"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="D21:O21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="D29:O29"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:M30"/>
   </mergeCells>
   <pageMargins left="0.43" right="0.26" top="0.45" bottom="0.46" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait"/>
@@ -8982,6 +8979,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010064B2BF85ECE1E44EA95F1573C2F0161A" ma:contentTypeVersion="27" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a41003f16fb81182e0268c720b4055c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0639b80-6b05-4a4f-b514-6f4abd6fb50f" xmlns:ns3="c848e2ba-a065-41ba-9956-d3396893a799" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a8dc79e468fc6cb94a0f406d213fec00" ns2:_="" ns3:_="">
     <xsd:import namespace="b0639b80-6b05-4a4f-b514-6f4abd6fb50f"/>
@@ -9309,15 +9315,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -9341,6 +9338,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C34AA48-961C-47B1-851A-7964AA1B13C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49AEFB24-550D-436F-A6D7-2D7C66C4D575}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9355,14 +9360,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C34AA48-961C-47B1-851A-7964AA1B13C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
